--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486262_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486262_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8925</v>
+        <v>1.6598</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.757</v>
+        <v>0.6712</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6494</v>
+        <v>0.9886</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5492</v>
+        <v>-0.9657</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6031</v>
+        <v>-0.666</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.1523</v>
+        <v>-0.2996</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8885</v>
+        <v>-0.956</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3084</v>
+        <v>-0.9942</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.1969</v>
+        <v>0.0382</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3393</v>
+        <v>-0.0097</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2947</v>
+        <v>0.3282</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0446</v>
+        <v>-0.3379</v>
       </c>
       <c r="P2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-0.435</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1817</v>
+        <v>-0.2647</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6117</v>
+        <v>-0.3929</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.1283</v>
       </c>
       <c r="V2" t="n">
-        <v>1.695</v>
+        <v>2.4552</v>
       </c>
       <c r="W2" t="n">
-        <v>1.695</v>
+        <v>2.4552</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4603</v>
+        <v>1.3237</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3792</v>
+        <v>0.6502</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0811</v>
+        <v>0.6735</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9657</v>
+        <v>1.2038</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.666</v>
+        <v>0.0181</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2996</v>
+        <v>1.1857</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.956</v>
+        <v>0.4772</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9942</v>
+        <v>0.0365</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0382</v>
+        <v>0.4407</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0097</v>
+        <v>0.7267</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3282</v>
+        <v>-0.0184</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3379</v>
+        <v>0.7451</v>
       </c>
       <c r="P3" t="n">
         <v>0.435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4642</v>
+        <v>-0.3151</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.173</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2207</v>
+        <v>-0.4882</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4413</v>
+        <v>1.2857</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8677</v>
+        <v>-1.1788</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5735</v>
+        <v>2.4645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3091</v>
+        <v>-0.5492</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0096</v>
+        <v>1.6031</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7004</v>
+        <v>-2.1523</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0799</v>
+        <v>-0.8885</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8249</v>
+        <v>1.3084</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7451</v>
+        <v>-2.1969</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.3393</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8153</v>
+        <v>0.2947</v>
       </c>
       <c r="O4" t="n">
         <v>0.0446</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4796</v>
+        <v>0.575</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6802</v>
+        <v>0.1899</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2006</v>
+        <v>0.3851</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1952</v>
+        <v>1.695</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5856</v>
+        <v>0.6423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06619999999999999</v>
+        <v>1.1884</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5194</v>
+        <v>-0.5461</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2038</v>
+        <v>0.5548</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0181</v>
+        <v>2.1533</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1857</v>
+        <v>-1.5985</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4772</v>
+        <v>1.2483</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0365</v>
+        <v>2.8715</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4407</v>
+        <v>-1.6232</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7267</v>
+        <v>-0.6935</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0184</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7451</v>
+        <v>0.0247</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0533</v>
+        <v>-1.0875</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.411</v>
+        <v>-0.4074</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6423</v>
+        <v>-0.6802</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4505</v>
+        <v>0.5618</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1199</v>
+        <v>0.2657</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6694</v>
+        <v>0.2961</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5548</v>
+        <v>0.3091</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1533</v>
+        <v>1.0096</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5985</v>
+        <v>-0.7004</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2483</v>
+        <v>1.0799</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8715</v>
+        <v>1.8249</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.6232</v>
+        <v>-0.7451</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6935</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.8153</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0247</v>
+        <v>0.0446</v>
       </c>
       <c r="P6" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.7401</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.2175</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.9576</v>
-      </c>
       <c r="S6" t="n">
-        <v>-1.2793</v>
+        <v>-0.3999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4759</v>
+        <v>0.0781</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8035</v>
+        <v>-0.478</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.6044</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0514</v>
+        <v>-0.0351</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.5693</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6823</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1679</v>
+        <v>-0.1619</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0601</v>
+        <v>-0.0264</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.228</v>
+        <v>-0.1355</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6446</v>
+        <v>-0.7234</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0693</v>
+        <v>-0.9323</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4247</v>
+        <v>0.2089</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0607</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1986</v>
+        <v>0.1199</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3425</v>
+        <v>-0.2055</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5411</v>
+        <v>0.3254</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9525</v>
+        <v>-0.9042</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7046</v>
+        <v>-0.9029</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2479</v>
+        <v>-0.0013</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6495</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3495</v>
+        <v>0.3978</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2656</v>
+        <v>0.0673</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0839</v>
+        <v>0.3305</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7575</v>
+        <v>-4.5078</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.613</v>
+        <v>-2.2093</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1445</v>
+        <v>-2.2986</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3517</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9283</v>
+        <v>-0.6787</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8784</v>
+        <v>-0.4747</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0499</v>
+        <v>-0.204</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9778</v>
+        <v>-5.55</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6635</v>
+        <v>-4.3282</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3143</v>
+        <v>-1.2218</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2081</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3119</v>
+        <v>-0.8841</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.3377</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6389</v>
+        <v>-0.5465</v>
       </c>
       <c r="V11" t="n">
         <v>0.3698</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6525</v>
+        <v>-5.9213</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3592</v>
+        <v>-4.8437</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2934</v>
+        <v>-1.0776</v>
       </c>
       <c r="G12" t="n">
         <v>-5.7329</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3547</v>
+        <v>-0.6234</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2379</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6012</v>
+        <v>-0.3854</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.7651</v>
+        <v>-12.7378</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.6822</v>
+        <v>-11.6548</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.083199999999999</v>
+        <v>-1.0831</v>
       </c>
       <c r="G13" t="n">
         <v>-13.1324</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5778</v>
+        <v>0.5778000000000009</v>
       </c>
       <c r="I13" t="n">
         <v>-13.7099</v>
@@ -1468,22 +1468,22 @@
         <v>13.0504</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.3502</v>
+        <v>-3.3226</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.6016</v>
+        <v>-1.5742</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7486</v>
+        <v>-1.7485</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6298</v>
+        <v>2.629800000000001</v>
       </c>
       <c r="W13" t="n">
         <v>11.6903</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.060499999999999</v>
+        <v>-9.060500000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1518</v>
+        <v>6.9206</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3152</v>
+        <v>4.8682</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8366</v>
+        <v>2.0524</v>
       </c>
       <c r="G14" t="n">
         <v>4.1019</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0499</v>
+        <v>0.8187</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8736</v>
+        <v>0.4266</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1763</v>
+        <v>0.392</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. MENCIA HERNANDEZ</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3558</v>
+        <v>4.3974</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0534</v>
+        <v>3.6659</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3024</v>
+        <v>0.7315</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8079</v>
+        <v>4.793</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6669</v>
+        <v>1.6605</v>
       </c>
       <c r="I15" t="n">
-        <v>0.141</v>
+        <v>3.1325</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8191000000000001</v>
+        <v>4.2823</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4877</v>
+        <v>2.0439</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6686</v>
+        <v>2.2384</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9888</v>
+        <v>0.5107</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1792</v>
+        <v>-0.3834</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8096</v>
+        <v>0.8941</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4402</v>
+        <v>-0.6354</v>
       </c>
       <c r="T15" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.6165</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3561</v>
+        <v>-0.0189</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3252</v>
+        <v>-0.1952</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1816</v>
+        <v>3.8191</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6659</v>
+        <v>1.7294</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5158</v>
+        <v>2.0897</v>
       </c>
       <c r="G16" t="n">
-        <v>4.793</v>
+        <v>1.1747</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6605</v>
+        <v>-0.6995</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1325</v>
+        <v>1.8742</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2823</v>
+        <v>-0.2451</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0439</v>
+        <v>0.1158</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2384</v>
+        <v>-0.3609</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5107</v>
+        <v>1.4198</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3834</v>
+        <v>-0.8153</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8941</v>
+        <v>2.2352</v>
       </c>
       <c r="P16" t="n">
         <v>0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8512</v>
+        <v>0.8841</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6165</v>
+        <v>0.6069</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2347</v>
+        <v>0.2773</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>Y. MENCIA HERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5358</v>
+        <v>3.6225</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7236</v>
+        <v>-0.0584</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8123</v>
+        <v>3.6809</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1747</v>
+        <v>1.8079</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6995</v>
+        <v>1.6669</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8742</v>
+        <v>0.141</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2451</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1158</v>
+        <v>1.4877</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3609</v>
+        <v>-0.6686</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4198</v>
+        <v>0.9888</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8153</v>
+        <v>0.1792</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2352</v>
+        <v>0.8096</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3991</v>
+        <v>0.7069</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.399</v>
+        <v>-0.0276</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0001</v>
+        <v>0.7345</v>
       </c>
       <c r="V17" t="n">
         <v>1.3252</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4552</v>
+        <v>1.3252</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8072</v>
+        <v>1.5197</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1418</v>
+        <v>-0.3055</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3346</v>
+        <v>1.8252</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6086</v>
+        <v>1.1322</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5998</v>
+        <v>-0.1523</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0088</v>
+        <v>1.2845</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2708</v>
+        <v>0.1259</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9011</v>
+        <v>0.1825</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6303</v>
+        <v>-0.0566</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3378</v>
+        <v>1.0063</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3013</v>
+        <v>-0.3348</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6391</v>
+        <v>1.3411</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7212</v>
+        <v>1.0602</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8736</v>
+        <v>0.6561</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8475</v>
+        <v>0.4041</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.3899</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5846</v>
+        <v>-0.1909</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7524999999999999</v>
+        <v>0.3595</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3371</v>
+        <v>-0.5503</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1322</v>
+        <v>2.6086</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1523</v>
+        <v>1.5998</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2845</v>
+        <v>1.0088</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1259</v>
+        <v>1.2708</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1825</v>
+        <v>1.9011</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0566</v>
+        <v>-0.6303</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0063</v>
+        <v>1.3378</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3348</v>
+        <v>-0.3013</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3411</v>
+        <v>1.6391</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1251</v>
+        <v>0.7231</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2091</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.6318</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2511</v>
+        <v>-0.2009</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9745</v>
+        <v>-0.8628</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7235</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2855</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0531</v>
+        <v>-0.003</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2894</v>
+        <v>0.2277</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5649999999999999</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7118</v>
+        <v>-0.4195</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9916</v>
+        <v>-1.8812</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2798</v>
+        <v>1.4617</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1359</v>
+        <v>-1.2229</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3989</v>
+        <v>-0.2038</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5348</v>
+        <v>-1.0192</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-1.2323</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9765</v>
+        <v>1.1925</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1292</v>
+        <v>-2.4248</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9833</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5776</v>
+        <v>-1.3963</v>
       </c>
       <c r="O21" t="n">
         <v>1.4056</v>
       </c>
       <c r="P21" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3904</v>
+        <v>0.9334</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1406</v>
+        <v>0.4386</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.531</v>
+        <v>0.4948</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3698</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2599</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9463</v>
+        <v>-0.708</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6185</v>
+        <v>-1.3269</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5648</v>
+        <v>0.6189</v>
       </c>
       <c r="G22" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.1359</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5413</v>
+        <v>-1.3989</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5498</v>
+        <v>2.5348</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4846</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5229</v>
+        <v>-1.9765</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0382</v>
+        <v>1.1292</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4932</v>
+        <v>1.9833</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0184</v>
+        <v>0.5776</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5116000000000001</v>
+        <v>1.4056</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9577</v>
+        <v>-0.3866</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1907</v>
+        <v>-0.1947</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.233</v>
+        <v>-0.192</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.2599</v>
+        <v>-0.3698</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X22" t="n">
         <v>-2.2599</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3701</v>
+        <v>-1.7722</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7752</v>
+        <v>-0.3873</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4051</v>
+        <v>-1.3849</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2229</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2038</v>
+        <v>-0.5413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0192</v>
+        <v>0.5498</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2323</v>
+        <v>-0.4846</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1925</v>
+        <v>-0.5229</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.4248</v>
+        <v>0.0382</v>
       </c>
       <c r="M23" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.4932</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3963</v>
+        <v>-0.0184</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4056</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0172</v>
+        <v>1.1317</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4554</v>
+        <v>1.1849</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4382</v>
+        <v>-0.0532</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5726</v>
+        <v>-2.4261</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9413</v>
+        <v>-4.7178</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3688</v>
+        <v>2.2917</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1221</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.233</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8099</v>
+        <v>-0.5864</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5769</v>
+        <v>0.4999</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.7649</v>
+        <v>14.5617</v>
       </c>
       <c r="E25" t="n">
-        <v>1.083299999999998</v>
+        <v>1.0831</v>
       </c>
       <c r="F25" t="n">
-        <v>12.682</v>
+        <v>13.4786</v>
       </c>
       <c r="G25" t="n">
         <v>13.1322</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5776999999999992</v>
+        <v>-0.5777000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>13.7098</v>
@@ -2380,16 +2380,16 @@
         <v>3.3244</v>
       </c>
       <c r="K25" t="n">
-        <v>3.348100000000001</v>
+        <v>3.3481</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.02380000000000004</v>
+        <v>-0.02380000000000027</v>
       </c>
       <c r="M25" t="n">
         <v>9.8079</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.9258</v>
+        <v>-3.925800000000001</v>
       </c>
       <c r="O25" t="n">
         <v>13.7336</v>
@@ -2404,19 +2404,19 @@
         <v>11.9627</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3501</v>
+        <v>5.1466</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7484</v>
+        <v>1.7485</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6016</v>
+        <v>3.398</v>
       </c>
       <c r="V25" t="n">
         <v>-2.6297</v>
       </c>
       <c r="W25" t="n">
-        <v>9.060499999999999</v>
+        <v>9.060500000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-11.6901</v>
